--- a/docs/feishu/jifen/首钢减重健康群「积分激励专属话术」 (1).xlsx
+++ b/docs/feishu/jifen/首钢减重健康群「积分激励专属话术」 (1).xlsx
@@ -1,59 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\惯能\群机器人定时推送\wecom_ops_console\docs\feishu\jifen\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3AAB634-7A9A-4733-851C-9A00E6092F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15800" windowWidth="28040" xWindow="4240" yWindow="640"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="6216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="首钢减重健康群「积分激励专属话术」" sheetId="2" r:id="rId5"/>
-    <sheet name="积分激励运营 投送阶段节点" sheetId="3" r:id="rId6"/>
+    <sheet name="首钢减重健康群「积分激励专属话术」" sheetId="2" r:id="rId1"/>
+    <sheet name="积分激励运营 投送阶段节点" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcMode="auto"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
+  <si>
     <r>
       <rPr>
         <sz val="9.75"/>
@@ -61,7 +35,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">@所有人 📊本周积分 &amp; 减重复盘来啦～恭喜本周</t>
+      <t>@所有人 📊本周积分 &amp; 减重复盘来啦～恭喜本周</t>
     </r>
     <r>
       <rPr>
@@ -71,7 +45,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">积分 TOP6</t>
+      <t>积分 TOP6</t>
     </r>
     <r>
       <rPr>
@@ -80,7 +54,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">的伙伴，持续领跑超厉害！
+      <t>的伙伴，持续领跑超厉害！
 表扬</t>
     </r>
     <r>
@@ -91,7 +65,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">连续 7 天稳定打卡学习</t>
+      <t>连续 7 天稳定打卡学习</t>
     </r>
     <r>
       <rPr>
@@ -100,7 +74,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">的家人，自律又优秀！
+      <t>的家人，自律又优秀！
 惊喜发现几位</t>
     </r>
     <r>
@@ -120,13 +94,12 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">的伙伴，积分猛涨，逆袭感拉满！
+      <t>的伙伴，积分猛涨，逆袭感拉满！
 断打卡后重新归队的小伙伴也很棒，坚持比完美更重要～还没跟上的家人下周一起加油，每天打卡就能追分！
 社群月度 PK 最新排名：XX，一起冲刺前 2 拿团队奖！</t>
     </r>
   </si>
   <si>
-    <t/>
     <r>
       <rPr>
         <sz val="9.75"/>
@@ -145,7 +118,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">积分前 6 名的小伙伴</t>
+      <t>积分前 6 名的小伙伴</t>
     </r>
     <r>
       <rPr>
@@ -174,7 +147,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">的伙伴们，你们的自律超亮眼，积分稳步上涨，为你们点赞！
+      <t>的伙伴们，你们的自律超亮眼，积分稳步上涨，为你们点赞！
 ✨ 好久不见的伙伴</t>
     </r>
     <r>
@@ -194,199 +167,560 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，积分一路上涨，太棒啦！减重任何时候开始都不晚～
+      <t>，积分一路上涨，太棒啦！减重任何时候开始都不晚～
 ❤️ 中途断卡又重新跟上的小伙伴，重新出发就很棒，慢慢追，一定能越来越好！
 还在潜水的家人也可以出来冒个泡～
 简单打卡就能涨积分，一起健康瘦下来！另外我们 20 个社群月度 PK 正在进行，每一分都为团队加分，一起冲呀！</t>
     </r>
   </si>
+  <si>
+    <t>首钢减重健康群「积分激励专属话术」</t>
+  </si>
+  <si>
+    <t>结合3 个月结营个人奖（金百花奖 / 绿草莓奖）、20 个社群月度 PK 团队奖，以及减重健康群的属性， 以下为3 套风格全部定制成适配场景的版本，直接复制发群，既能激励活跃，又贴合项目调性。</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>话术</t>
+  </si>
+  <si>
+    <t>【专业正式版】（适配首钢国企群、严肃健康管理场景）</t>
+  </si>
+  <si>
+    <t>【温柔陪伴版】</t>
+  </si>
+  <si>
+    <t>【活泼接地气版】</t>
+  </si>
+  <si>
+    <t>排名前几名专属激励话术
+（前 3 / 前 6 / 前十）
+个人榜前 6 名
+（金百花奖冲刺）专属激励</t>
+  </si>
+  <si>
+    <t>群内前 6 名的小伙伴注意啦！现在积分咬得非常紧，再坚持几天，大奖就是你们的！继续保持打卡、互动，别被后面的人反超～</t>
+  </si>
+  <si>
+    <t>@所有人 【积分冲刺提醒】
+目前个人积分榜前 6 名的伙伴，已经稳稳站在「金百花奖」第一梯队！距离 3 个月结营还有 XX 天，大家的积分咬得非常紧，只要继续保持每日打卡、认真学习健康课件、积极参与群内互动，最终大奖就会稳稳到手。
+也请前 6 名的伙伴继续做好榜样，带动全群一起养成健康减重的好习惯，为咱们首钢减重项目的成果添砖加瓦！</t>
+  </si>
+  <si>
+    <t>群里积分前六位的小伙伴真的太优秀啦🥰
+现在离 3 个月结营越来越近，大家的积分咬得紧紧的，再坚持坚持，「金百花奖」大奖就在眼前啦！继续保持每天打卡、认真学习，稳稳冲刺，你们超有希望，也给群里的姐妹们做了最好的榜样～</t>
+  </si>
+  <si>
+    <t>⚠️前排大佬请注意！⚠️
+个人积分 TOP6 已经锁死「金百花奖」冲线区！后面的人正在疯狂追赶，千万别翻车！再努努力，3 个月结营大奖直接抱回家，稳住就是胜利！</t>
+  </si>
+  <si>
+    <t>目前群内积分 TOP3 已经遥遥领先，不愧是咱们群的标杆！保持这个节奏，稳稳冲刺最终大奖，也给大家做个好榜样！</t>
+  </si>
+  <si>
+    <t>前十的伙伴们差距很小，稍微多互动、多打卡就能往前冲一冲，最终排名还没定，冲一把就能拿到更好奖励！</t>
+  </si>
+  <si>
+    <t>前几名的同学已经把节奏焊死了！每天稳定输出、认真学习，这种坚持真的值得所有人学习，继续稳住！</t>
+  </si>
+  <si>
+    <t>连续稳定活跃用户
+（每天打卡 / 看课件 / 积极发言）</t>
+  </si>
+  <si>
+    <t>必须点名表扬 XX！连续多天稳定打卡、认真看课件，积分稳步上涨，自律力拉满，是群里妥妥的学习榜样～</t>
+  </si>
+  <si>
+    <t>特别表扬近期连续多日坚持打卡、认真学习减重课件的伙伴们！
+每日稳定参与、持续积累，不仅积分稳步提升，更用自律践行了健康生活方式，这份坚持值得全体成员学习。减重没有捷径，每一次打卡、每一页课件，都是在为自己的健康和身材打基础，继续保持，结营时一定会收获满意的成果！</t>
+  </si>
+  <si>
+    <t>每天都能准时看到你们打卡、认真看课件，真的特别暖心❤️
+一步一步积累，积分慢慢上涨，你们的坚持，所有人都看在眼里、记在心里。减重是一场温柔的修行，谢谢你们用自律，给了大家一起变好的力量，为你们点赞，继续加油呀！</t>
+  </si>
+  <si>
+    <t>实名表扬群里的卷王选手！
+天天打卡、天天看课，积分一路狂飙，这自律程度我直接 respect！全场最佳就是你，减重路上的标杆，给我焊死在榜一！</t>
+  </si>
+  <si>
+    <t>每天都能看到 XX 准时出现，坚持学习、积极互动，这种长期稳定的状态太赞了！积分就是最好的证明，继续保持！</t>
+  </si>
+  <si>
+    <t>像 XX 这样每天坚持打卡、完成学习任务的伙伴，积分自然一路上涨，付出都会有回报，大家多向他看齐！</t>
+  </si>
+  <si>
+    <t>持续活跃、持续输出，积分排名一路稳中有升，为 XX 的坚持点赞！跟着节奏走，大奖离你越来越近～</t>
+  </si>
+  <si>
+    <t>异常增长 / 突然爆发型
+（很久没动静，突然活跃）</t>
+  </si>
+  <si>
+    <t>惊喜发现！XX 好久没出现，今天突然回归打卡、积极互动，积分直接起飞，这波回归太亮眼啦！</t>
+  </si>
+  <si>
+    <t>近期发现部分伙伴前期活跃度不高，甚至连续多日未打卡，近期突然恢复打卡、积极互动，积分出现明显上涨。
+行动永远不晚，减重从来没有 “来不及”，只要从今天开始坚持，依然有机会冲刺「金百花奖」，也能在 3 个月内收获理想的减重效果。欢迎大家回归，跟上大部队，一起健康瘦下来！</t>
+  </si>
+  <si>
+    <t>好久不见的伙伴最近突然活跃起来啦，连续打卡、积极发言，积分一下子就上来了✨
+真的太为你开心了！减重从来没有 “太晚了”，只要愿意开始，什么时候都不晚。欢迎回来，我们一起慢慢走、稳稳瘦，一起拿到属于自己的好成绩！</t>
+  </si>
+  <si>
+    <t>惊现黑马！这位朋友前几天还隐身，最近突然上线猛冲打卡，积分直接起飞🚀
+这是准备悄悄惊艳所有人吗？！欢迎回归，冲就完事了，「金百花奖」还有位置，给我冲！</t>
+  </si>
+  <si>
+    <t>欢迎 XX 强势回归！沉寂多天后突然发力，积分暴涨，看来是准备冲刺排名了，期待接下来的表现！</t>
+  </si>
+  <si>
+    <t>发现一位 “潜力股”——XX 之前活跃度不高，这几天突然连续打卡、认真学习，积分一路猛涨，太让人惊喜了！</t>
+  </si>
+  <si>
+    <t>只要开始行动，永远都不晚！XX 用实际行动证明，哪怕之前落下，现在跟上节奏照样能冲排名，大家都可以学起来！</t>
+  </si>
+  <si>
+    <t>中途掉队但重新跟上
+（断打卡后恢复）</t>
+  </si>
+  <si>
+    <t>虽然中间短暂休息，但 XX 现在已经重新回归打卡，状态慢慢回来啦！跟上大部队，积分还能继续往上冲！</t>
+  </si>
+  <si>
+    <t>部分伙伴虽曾短暂中断打卡，但已重新跟上节奏，恢复日常参与。
+减重路上偶尔的停顿不可怕，重新出发才最难得。欢迎归队，慢慢跟上每日打卡、学习的节奏，积分还有大幅提升空间，我们一起稳步减重，健康变美！</t>
+  </si>
+  <si>
+    <t>中间偶尔停下没关系，重要的是你又重新出发了呀💪
+欢迎回来，不用急着追进度，慢慢跟上每天打卡、学习的节奏就好。我们一起往前冲，积分会涨，体重会降，你想要的，时间都会给你！</t>
+  </si>
+  <si>
+    <t>失踪人口回归啦！虽然断更了几天，但现在满血复活，冲就完事了！
+积分还能追，体重还能降，别摆烂，跟紧大部队，结营一起瘦成闪电！</t>
+  </si>
+  <si>
+    <t>断卡不可怕，重新开始最难得！XX 已经重新坚持起来，为这份坚持点赞，继续加油往前追！</t>
+  </si>
+  <si>
+    <t>欢迎 XX 归队！之前落下的进度，现在一点点补回来，排名还有机会，一起往前冲！</t>
+  </si>
+  <si>
+    <t>积分上升明显 / 进步飞快</t>
+  </si>
+  <si>
+    <t>最近群里好多伙伴积分涨得飞快，明显是更用心参与了！继续保持这个势头，排名还能再往上冲！</t>
+  </si>
+  <si>
+    <t>进步看得见！XX 这几天活跃度明显提升，打卡、互动样样不落，积分一路飙升，太棒了！</t>
+  </si>
+  <si>
+    <t>只要每天多花一点时间参与，积分差距很快就能追上，XX 就是最好的例子，大家都可以试试！</t>
+  </si>
+  <si>
+    <t>提醒观望 / 潜水用户
+（温和带动）</t>
+  </si>
+  <si>
+    <t>还在观望的伙伴可以动起来啦！每天简单打卡、参与互动，积分就能慢慢涨，排名靠前奖励更丰厚～</t>
+  </si>
+  <si>
+    <t>仍在观望的伙伴请积极参与日常打卡与互动：
+个人积分榜实时更新，3 个月结营的「金百花奖」「绿草莓奖」排名还未最终确定，现在开始行动完全来得及。越活跃，积分越高，不仅能冲刺丰厚奖励，更能在群内氛围的带动下，养成受益终身的健康减重习惯！</t>
+  </si>
+  <si>
+    <t>还在默默潜水的小伙伴，也可以试着出来冒个泡呀～
+每天简单打个卡、在群里说说话，积分就会慢慢涨，还能跟着大家一起养成健康减重的好习惯。现在参与完全来得及，一起加入进来，我们互相陪伴，一起健康变瘦变美！</t>
+  </si>
+  <si>
+    <t>还在潜水的家人们别蹲了！出来打卡、唠唠嗑，积分蹭蹭涨！
+再不活跃，「金百花奖」就没你的份了，体重也掉不下来！赶紧动起来，跟着大部队一起瘦，一起拿奖！</t>
+  </si>
+  <si>
+    <t>积分排名实时更新，现在参与完全来得及！随手打卡、积极发言，既能学到东西，又能冲奖，一举两得！</t>
+  </si>
+  <si>
+    <t>20 个社群月度 PK 团队奖激励</t>
+  </si>
+  <si>
+    <t>@所有社群负责人 &amp; 群成员 【月度社群 PK 提醒】
+20 个社群的综合排名（打卡率 / 减重率 / 积分率）每月更新，每月发放团队奖！
+个人的坚持汇聚成团队的力量，每一次打卡、每一分积分，都在为咱们社群的排名助力。请大家积极活跃、认真减重，一起冲刺月度前 2 名，拿团队大奖，为咱们的社群争光！</t>
+  </si>
+  <si>
+    <t>家人们，咱们 20 个社群的月度 PK 赛每月都有奖励哦🥳
+咱们社群的排名，靠的是每一个人的打卡、每一分积分、每一斤的减重成果！大家一起活跃起来、认真减重，一起冲刺月度前 2 名，拿团队大奖，咱们一起赢！</t>
+  </si>
+  <si>
+    <t>家人们！20 个社群月度 PK 赛开卷了！
+咱们社群的排名，就看你们的打卡率、减重率、积分率！每一分都算数，每一斤都关键！一起冲月度前 2，拿团队大奖，给咱们社群长脸！</t>
+  </si>
+  <si>
+    <t>别让自己一直潜水哦，群里氛围这么好，跟着大家一起活跃起来，积分和收获都会有的！</t>
+  </si>
+  <si>
+    <t>今日个人积分榜单已更新！看看自己离「金百花奖」还有多远？多打一次卡、多学一页课件，积分就多一分，大奖就更近一步！</t>
+  </si>
+  <si>
+    <t>每日氛围带动通用话术
+【每日通用氛围带动话术】
+（适配日常发榜、复盘）</t>
+  </si>
+  <si>
+    <t>积分排名实时更新中，越活跃越靠前，坚持打卡、积极互动，大奖就在前方！</t>
+  </si>
+  <si>
+    <t>20 个社群月度 PK 排名实时更新！每一个人的打卡，都在为咱们社群加分！一起活跃起来，冲月度前 2，拿团队大奖！</t>
+  </si>
+  <si>
+    <t>今日积分榜单已更新，看看自己排在第几？往前多冲几名，奖励又近一步！</t>
+  </si>
+  <si>
+    <t>积分就是努力的证明！越活跃，越瘦得快，越能拿大奖！家人们，冲就完事了！</t>
+  </si>
+  <si>
+    <t>群内积分靠大家一起活跃，你多出现一次，排名就多一份希望，一起动起来！</t>
+  </si>
+  <si>
+    <t>结营倒计时 XX 天！前 6 名稳住，后 6 名逆袭，中间的伙伴往前冲，咱们一起健康减重，一起拿奖！</t>
+  </si>
+  <si>
+    <t>【反向激励专属话术】
+（适配后 6 名「绿草莓奖」幽默激励）</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 正式版</t>
+  </si>
+  <si>
+    <t>温柔版</t>
+  </si>
+  <si>
+    <t>活泼版</t>
+  </si>
+  <si>
+    <t>个人积分榜后 6 名的伙伴请注意：
+本次结营设置「绿草莓奖」幽默反向激励，希望大家以此为契机，重新调整减重节奏，跟上每日打卡、学习的进度，在后续的健康管理中迎头赶上，收获理想的减重成果。</t>
+  </si>
+  <si>
+    <t>积分暂时靠后的小伙伴们别灰心呀～
+3 个月的旅程还没结束，现在开始行动，积分和体重都能追上来！我们一起慢慢调整，互相陪伴，下一次榜单一定能看到你们的进步！</t>
+  </si>
+  <si>
+    <t>家人们！后 6 名的「绿草莓奖」已经就位！
+别摆烂了！再不打卡、再不减重，就要拿反向奖励了！赶紧动起来，把积分冲上去，把体重降下来，逆袭就在下一个榜单！</t>
+  </si>
+  <si>
+    <t>减重健康群・积分激励运营
+发榜时间：每日早 8:00 早安分享后立即发送</t>
+  </si>
+  <si>
+    <t>阶段节点</t>
+  </si>
+  <si>
+    <t>执行时间</t>
+  </si>
+  <si>
+    <t>核心动作</t>
+  </si>
+  <si>
+    <t>群内话术（可直接复制）</t>
+  </si>
+  <si>
+    <t>配套 1v1 动作</t>
+  </si>
+  <si>
+    <t>第一阶段：每日发榜（日常运营）</t>
+  </si>
+  <si>
+    <t>每日早 8:00早安后立刻发</t>
+  </si>
+  <si>
+    <t>1. 发今日积分榜
+2. 表扬前 6 名
+3. 表扬连续打卡
+4. 鼓励回归用户
+5. 提醒潜水成员
+6. 提社群月度 PK</t>
+  </si>
+  <si>
+    <t>1. 私发 TOP3：鼓励稳住排名
+2. 私发连续打卡：肯定坚持
+3. 私发 3 天未打卡：温和提醒</t>
+  </si>
+  <si>
+    <t>第二阶段：每周复盘（深度激活）</t>
+  </si>
+  <si>
+    <t>每周日晚 19:30</t>
+  </si>
+  <si>
+    <t>1. 本周积分总结
+2. 表扬周 TOP6
+3. 表扬积分暴涨用户
+4. 鼓励掉队回归
+5. 同步社群 PK 排名
+6. 轻科普减重知识点</t>
+  </si>
+  <si>
+    <t>1. 表扬进步最快用户
+2. 邀请减重效果好的分享
+3. 连续 2 周未打卡：1v1 关怀</t>
+  </si>
+  <si>
+    <t>结营冲刺
+（前 14～7 天）</t>
+  </si>
+  <si>
+    <t>每日早 8:00</t>
+  </si>
+  <si>
+    <t>倒计时提醒 + 动员前 6 稳住、中间冲刺、后段逆袭</t>
+  </si>
+  <si>
+    <t>@所有人
+ ⚡金百花奖冲刺倒计时 XX 天前 6 名的伙伴继续稳住，别被反超！
+中间梯队再冲一冲，完全有机会进前 6！暂时靠后的伙伴正是逆袭好时机，每天打卡就能追分！
+社群 PK 最后冲刺，一起为团队争光！</t>
+  </si>
+  <si>
+    <t>重点用户群内 @提醒</t>
+  </si>
+  <si>
+    <t>结营冲刺
+（前 7～3 天）</t>
+  </si>
+  <si>
+    <t>早 8:00 发榜 +晚再补一条冲刺</t>
+  </si>
+  <si>
+    <t>早晚双重动员强化紧迫感</t>
+  </si>
+  <si>
+    <t>早 8:00：早安～今日积分榜已更新！冲刺最后阶段，每一分都关键，前 6 稳住、中间猛冲、后面逆袭！
+晚提醒：最后 XX 天冲金百花奖！今天多打卡、多互动，排名就能再往前，大奖近在眼前！</t>
+  </si>
+  <si>
+    <t>对差几分进前 6 的用户群内艾特鼓励</t>
+  </si>
+  <si>
+    <t>结营前 1 天</t>
+  </si>
+  <si>
+    <t>早 8:00</t>
+  </si>
+  <si>
+    <t>最终冲刺提醒最后打卡号召</t>
+  </si>
+  <si>
+    <t>@所有人 
+🎉最后 1 天冲刺！今天的打卡将决定最终排名，前 6 名稳住阵脚，所有人再努力一把，不留遗憾！感谢一路陪伴，明天公布最终榜单与金百花奖、绿草莓奖、社群 PK 大奖！</t>
+  </si>
+  <si>
+    <t>群内@用户 提醒 TOP10 务必打卡</t>
+  </si>
+  <si>
+    <t>结营当天</t>
+  </si>
+  <si>
+    <t>公布最终榜单获奖公示</t>
+  </si>
+  <si>
+    <t>@所有人 🎊3 个月结营・最终积分榜单公布
+🏆金百花奖（前 6）：XX🍀
+绿草莓奖（后 6）：XX
+团队月度 PK 获奖社群：XX
+感谢大家的坚持，减重不是终点，而是健康生活的开始！</t>
+  </si>
+  <si>
+    <t>获奖用户恭喜【绿草莓用户】温柔鼓励</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="20">
     <fill>
-      <patternFill patternType="none">
-        <fgColor/>
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor/>
-        <bgColor/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9F5D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9F5D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9F5D6"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFECE2FE"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFECE2FE"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDDDEF"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDDDEF"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDDDEF"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7A0F4B"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7A0F4B"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF6C6"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF6C6"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF6C6"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFAF1D1"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF006185"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
@@ -816,114 +1150,117 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
-    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+  <cellXfs count="34">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="7" fillId="4" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="8" fillId="5" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="11" fillId="6" fontId="4" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="13" fillId="7" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="14" fillId="8" fontId="4" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="15" fillId="9" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="16" fillId="10" fontId="4" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="17" fillId="11" fontId="5" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="18" fillId="12" fontId="6" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="19" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="20" fillId="13" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="21" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="22" fillId="14" fontId="7" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="23" fillId="15" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="24" fillId="16" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="25" fillId="0" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="26" fillId="0" fontId="7" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="28" fillId="0" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="29" fillId="0" fontId="3" numFmtId="0" xfId="0">
-      <alignment vertical="top" wrapText="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="30" fillId="17" fontId="7" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="31" fillId="18" fontId="7" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="32" fillId="19" fontId="5" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -936,7 +1273,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -952,9 +1289,15 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="ywQagl"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="ywQagl">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="false"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -968,16 +1311,18 @@
           <a:off x="0" y="0"/>
           <a:ext cx="0" cy="0"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData fLocksWithSheet="false" fPrintsWithSheet="true"/>
+    <xdr:clientData fLocksWithSheet="0"/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1271,31 +1616,31 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35241BB3-6A42-4B6A-A4CB-BA7B9ADDBF9D}">
   <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="19"/>
+  <dimension ref="A1:T201"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="6" min="6" style="0" width="46"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="56" customWidth="1"/>
+    <col min="4" max="4" width="66" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row customHeight="true" ht="34" r="1">
-      <c r="A1" s="17" t="str">
-        <v>首钢减重健康群「积分激励专属话术」</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+    <row r="1" spans="1:20" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1311,15 +1656,15 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row customHeight="true" ht="29" r="2">
-      <c r="A2" s="16" t="str">
-        <v>结合3 个月结营个人奖（金百花奖 / 绿草莓奖）、20 个社群月度 PK 团队奖，以及减重健康群的属性， 以下为3 套风格全部定制成适配场景的版本，直接复制发群，既能激励活跃，又贴合项目调性。</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
+    <row r="2" spans="1:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1335,65 +1680,58 @@
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
     </row>
-    <row customHeight="true" ht="42.18455228981545" r="3">
-      <c r="A3" s="11" t="str">
-        <v>序号</v>
-      </c>
-      <c r="B3" s="13" t="str">
-        <v>类型</v>
-      </c>
-      <c r="C3" s="11" t="str">
-        <v>话术</v>
-      </c>
-      <c r="D3" s="11" t="str">
-        <v>【专业正式版】（适配首钢国企群、严肃健康管理场景）</v>
-      </c>
-      <c r="E3" s="11" t="str">
-        <v>【温柔陪伴版】</v>
-      </c>
-      <c r="F3" s="11" t="str">
-        <v>【活泼接地气版】</v>
-      </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-    </row>
-    <row r="4">
+    <row r="3" spans="1:20" ht="42.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+    </row>
+    <row r="4" spans="1:20" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="str">
-        <v>排名前几名专属激励话术
-（前 3 / 前 6 / 前十）
-个人榜前 6 名
-（金百花奖冲刺）专属激励</v>
-      </c>
-      <c r="C4" s="4" t="str">
-        <v>群内前 6 名的小伙伴注意啦！现在积分咬得非常紧，再坚持几天，大奖就是你们的！继续保持打卡、互动，别被后面的人反超～</v>
-      </c>
-      <c r="D4" s="4" t="str">
-        <v>@所有人 【积分冲刺提醒】
-目前个人积分榜前 6 名的伙伴，已经稳稳站在「金百花奖」第一梯队！距离 3 个月结营还有 XX 天，大家的积分咬得非常紧，只要继续保持每日打卡、认真学习健康课件、积极参与群内互动，最终大奖就会稳稳到手。
-也请前 6 名的伙伴继续做好榜样，带动全群一起养成健康减重的好习惯，为咱们首钢减重项目的成果添砖加瓦！</v>
-      </c>
-      <c r="E4" s="4" t="str">
-        <v>群里积分前六位的小伙伴真的太优秀啦🥰
-现在离 3 个月结营越来越近，大家的积分咬得紧紧的，再坚持坚持，「金百花奖」大奖就在眼前啦！继续保持每天打卡、认真学习，稳稳冲刺，你们超有希望，也给群里的姐妹们做了最好的榜样～</v>
-      </c>
-      <c r="F4" s="4" t="str">
-        <v>⚠️前排大佬请注意！⚠️
-个人积分 TOP6 已经锁死「金百花奖」冲线区！后面的人正在疯狂追赶，千万别翻车！再努努力，3 个月结营大奖直接抱回家，稳住就是胜利！</v>
+      <c r="B4" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1410,13 +1748,13 @@
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="4" t="str">
-        <v>目前群内积分 TOP3 已经遥遥领先，不愧是咱们群的标杆！保持这个节奏，稳稳冲刺最终大奖，也给大家做个好榜样！</v>
+      <c r="B5" s="30"/>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -1436,14 +1774,13 @@
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>3</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="4" t="str">
-        <v>前十的伙伴们差距很小，稍微多互动、多打卡就能往前冲一冲，最终排名还没定，冲一把就能拿到更好奖励！
-</v>
+      <c r="B6" s="30"/>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -1463,13 +1800,13 @@
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="4" t="str">
-        <v>前几名的同学已经把节奏焊死了！每天稳定输出、认真学习，这种坚持真的值得所有人学习，继续稳住！</v>
+      <c r="B7" s="30"/>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -1489,28 +1826,24 @@
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:20" ht="66" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="str">
-        <v>连续稳定活跃用户
-（每天打卡 / 看课件 / 积极发言）</v>
-      </c>
-      <c r="C8" s="9" t="str">
-        <v>必须点名表扬 XX！连续多天稳定打卡、认真看课件，积分稳步上涨，自律力拉满，是群里妥妥的学习榜样～</v>
-      </c>
-      <c r="D8" s="9" t="str">
-        <v>特别表扬近期连续多日坚持打卡、认真学习减重课件的伙伴们！
-每日稳定参与、持续积累，不仅积分稳步提升，更用自律践行了健康生活方式，这份坚持值得全体成员学习。减重没有捷径，每一次打卡、每一页课件，都是在为自己的健康和身材打基础，继续保持，结营时一定会收获满意的成果！</v>
-      </c>
-      <c r="E8" s="9" t="str">
-        <v>每天都能准时看到你们打卡、认真看课件，真的特别暖心❤️
-一步一步积累，积分慢慢上涨，你们的坚持，所有人都看在眼里、记在心里。减重是一场温柔的修行，谢谢你们用自律，给了大家一起变好的力量，为你们点赞，继续加油呀！</v>
-      </c>
-      <c r="F8" s="9" t="str">
-        <v>实名表扬群里的卷王选手！
-天天打卡、天天看课，积分一路狂飙，这自律程度我直接 respect！全场最佳就是你，减重路上的标杆，给我焊死在榜一！</v>
+      <c r="B8" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1527,17 +1860,17 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>6</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="9" t="str">
-        <v>每天都能看到 XX 准时出现，坚持学习、积极互动，这种长期稳定的状态太赞了！积分就是最好的证明，继续保持！</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1553,17 +1886,17 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>7</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="9" t="str">
-        <v>像 XX 这样每天坚持打卡、完成学习任务的伙伴，积分自然一路上涨，付出都会有回报，大家多向他看齐！</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1579,17 +1912,17 @@
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>8</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="9" t="str">
-        <v>持续活跃、持续输出，积分排名一路稳中有升，为 XX 的坚持点赞！跟着节奏走，大奖离你越来越近～</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1605,29 +1938,24 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:20" ht="66" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B12" s="6" t="str">
-        <v>异常增长 / 突然爆发型
-（很久没动静，突然活跃）</v>
-      </c>
-      <c r="C12" s="4" t="str">
-        <v>惊喜发现！XX 好久没出现，今天突然回归打卡、积极互动，积分直接起飞，这波回归太亮眼啦！</v>
-      </c>
-      <c r="D12" s="4" t="str">
-        <v>近期发现部分伙伴前期活跃度不高，甚至连续多日未打卡，近期突然恢复打卡、积极互动，积分出现明显上涨。
-行动永远不晚，减重从来没有 “来不及”，只要从今天开始坚持，依然有机会冲刺「金百花奖」，也能在 3 个月内收获理想的减重效果。欢迎大家回归，跟上大部队，一起健康瘦下来！</v>
-      </c>
-      <c r="E12" s="4" t="str">
-        <v>好久不见的伙伴最近突然活跃起来啦，连续打卡、积极发言，积分一下子就上来了✨
-真的太为你开心了！减重从来没有 “太晚了”，只要愿意开始，什么时候都不晚。欢迎回来，我们一起慢慢走、稳稳瘦，一起拿到属于自己的好成绩！</v>
-      </c>
-      <c r="F12" s="4" t="str">
-        <v>惊现黑马！这位朋友前几天还隐身，最近突然上线猛冲打卡，积分直接起飞🚀
-这是准备悄悄惊艳所有人吗？！欢迎回归，冲就完事了，「金百花奖」还有位置，给我冲！
-</v>
+      <c r="B12" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1644,13 +1972,13 @@
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>10</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="4" t="str">
-        <v>欢迎 XX 强势回归！沉寂多天后突然发力，积分暴涨，看来是准备冲刺排名了，期待接下来的表现！</v>
+      <c r="B13" s="30"/>
+      <c r="C13" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -1670,13 +1998,13 @@
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>11</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="4" t="str">
-        <v>发现一位 “潜力股”——XX 之前活跃度不高，这几天突然连续打卡、认真学习，积分一路猛涨，太让人惊喜了！</v>
+      <c r="B14" s="30"/>
+      <c r="C14" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -1696,13 +2024,13 @@
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>12</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="4" t="str">
-        <v>只要开始行动，永远都不晚！XX 用实际行动证明，哪怕之前落下，现在跟上节奏照样能冲排名，大家都可以学起来！</v>
+      <c r="B15" s="30"/>
+      <c r="C15" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -1722,28 +2050,24 @@
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:20" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>13</v>
       </c>
-      <c r="B16" s="10" t="str">
-        <v>中途掉队但重新跟上
-（断打卡后恢复）</v>
-      </c>
-      <c r="C16" s="9" t="str">
-        <v>虽然中间短暂休息，但 XX 现在已经重新回归打卡，状态慢慢回来啦！跟上大部队，积分还能继续往上冲！</v>
-      </c>
-      <c r="D16" s="9" t="str">
-        <v>部分伙伴虽曾短暂中断打卡，但已重新跟上节奏，恢复日常参与。
-减重路上偶尔的停顿不可怕，重新出发才最难得。欢迎归队，慢慢跟上每日打卡、学习的节奏，积分还有大幅提升空间，我们一起稳步减重，健康变美！</v>
-      </c>
-      <c r="E16" s="9" t="str">
-        <v>中间偶尔停下没关系，重要的是你又重新出发了呀💪
-欢迎回来，不用急着追进度，慢慢跟上每天打卡、学习的节奏就好。我们一起往前冲，积分会涨，体重会降，你想要的，时间都会给你！</v>
-      </c>
-      <c r="F16" s="9" t="str">
-        <v>失踪人口回归啦！虽然断更了几天，但现在满血复活，冲就完事了！
-积分还能追，体重还能降，别摆烂，跟紧大部队，结营一起瘦成闪电！</v>
+      <c r="B16" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1760,17 +2084,17 @@
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>14</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="9" t="str">
-        <v>断卡不可怕，重新开始最难得！XX 已经重新坚持起来，为这份坚持点赞，继续加油往前追！</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1786,17 +2110,17 @@
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>15</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="9" t="str">
-        <v>欢迎 XX 归队！之前落下的进度，现在一点点补回来，排名还有机会，一起往前冲！</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1812,15 +2136,15 @@
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>16</v>
       </c>
-      <c r="B19" s="6" t="str">
-        <v>积分上升明显 / 进步飞快</v>
-      </c>
-      <c r="C19" s="4" t="str">
-        <v>最近群里好多伙伴积分涨得飞快，明显是更用心参与了！继续保持这个势头，排名还能再往上冲！</v>
+      <c r="B19" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -1840,13 +2164,13 @@
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>17</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="4" t="str">
-        <v>进步看得见！XX 这几天活跃度明显提升，打卡、互动样样不落，积分一路飙升，太棒了！</v>
+      <c r="B20" s="30"/>
+      <c r="C20" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -1866,13 +2190,13 @@
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>18</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="4" t="str">
-        <v>只要每天多花一点时间参与，积分差距很快就能追上，XX 就是最好的例子，大家都可以试试！</v>
+      <c r="B21" s="30"/>
+      <c r="C21" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -1892,28 +2216,24 @@
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:20" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>19</v>
       </c>
-      <c r="B22" s="10" t="str">
-        <v>提醒观望 / 潜水用户
-（温和带动）</v>
-      </c>
-      <c r="C22" s="9" t="str">
-        <v>还在观望的伙伴可以动起来啦！每天简单打卡、参与互动，积分就能慢慢涨，排名靠前奖励更丰厚～</v>
-      </c>
-      <c r="D22" s="9" t="str">
-        <v>仍在观望的伙伴请积极参与日常打卡与互动：
-个人积分榜实时更新，3 个月结营的「金百花奖」「绿草莓奖」排名还未最终确定，现在开始行动完全来得及。越活跃，积分越高，不仅能冲刺丰厚奖励，更能在群内氛围的带动下，养成受益终身的健康减重习惯！</v>
-      </c>
-      <c r="E22" s="9" t="str">
-        <v>还在默默潜水的小伙伴，也可以试着出来冒个泡呀～
-每天简单打个卡、在群里说说话，积分就会慢慢涨，还能跟着大家一起养成健康减重的好习惯。现在参与完全来得及，一起加入进来，我们互相陪伴，一起健康变瘦变美！</v>
-      </c>
-      <c r="F22" s="9" t="str">
-        <v>还在潜水的家人们别蹲了！出来打卡、唠唠嗑，积分蹭蹭涨！
-再不活跃，「金百花奖」就没你的份了，体重也掉不下来！赶紧动起来，跟着大部队一起瘦，一起拿奖！</v>
+      <c r="B22" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1930,17 +2250,17 @@
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>20</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="9" t="str">
-        <v>积分排名实时更新，现在参与完全来得及！随手打卡、积极发言，既能学到东西，又能冲奖，一举两得！</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1956,26 +2276,22 @@
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
     </row>
-    <row customHeight="true" ht="91" r="24">
+    <row r="24" spans="1:20" ht="91.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>21</v>
       </c>
-      <c r="B24" s="6" t="str">
-        <v>20 个社群月度 PK 团队奖激励</v>
+      <c r="B24" s="30" t="s">
+        <v>51</v>
       </c>
       <c r="C24" s="4"/>
-      <c r="D24" s="4" t="str">
-        <v>@所有社群负责人 &amp; 群成员 【月度社群 PK 提醒】
-20 个社群的综合排名（打卡率 / 减重率 / 积分率）每月更新，每月发放团队奖！
-个人的坚持汇聚成团队的力量，每一次打卡、每一分积分，都在为咱们社群的排名助力。请大家积极活跃、认真减重，一起冲刺月度前 2 名，拿团队大奖，为咱们的社群争光！</v>
-      </c>
-      <c r="E24" s="4" t="str">
-        <v>家人们，咱们 20 个社群的月度 PK 赛每月都有奖励哦🥳
-咱们社群的排名，靠的是每一个人的打卡、每一分积分、每一斤的减重成果！大家一起活跃起来、认真减重，一起冲刺月度前 2 名，拿团队大奖，咱们一起赢！</v>
-      </c>
-      <c r="F24" s="4" t="str">
-        <v>家人们！20 个社群月度 PK 赛开卷了！
-咱们社群的排名，就看你们的打卡率、减重率、积分率！每一分都算数，每一斤都关键！一起冲月度前 2，拿团队大奖，给咱们社群长脸！</v>
+      <c r="D24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1992,16 +2308,16 @@
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>22</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="4" t="str">
-        <v>别让自己一直潜水哦，群里氛围这么好，跟着大家一起活跃起来，积分和收获都会有的！</v>
-      </c>
-      <c r="D25" s="4" t="str">
-        <v>今日个人积分榜单已更新！看看自己离「金百花奖」还有多远？多打一次卡、多学一页课件，积分就多一分，大奖就更近一步！</v>
+      <c r="B25" s="30"/>
+      <c r="C25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -2020,23 +2336,21 @@
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>23</v>
       </c>
-      <c r="B26" s="10" t="str">
-        <v>每日氛围带动通用话术
-【每日通用氛围带动话术】
-（适配日常发榜、复盘）</v>
-      </c>
-      <c r="C26" s="9" t="str">
-        <v>积分排名实时更新中，越活跃越靠前，坚持打卡、积极互动，大奖就在前方！</v>
-      </c>
-      <c r="D26" s="9" t="str">
-        <v>20 个社群月度 PK 排名实时更新！每一个人的打卡，都在为咱们社群加分！一起活跃起来，冲月度前 2，拿团队大奖！</v>
-      </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
+      <c r="B26" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -2052,19 +2366,19 @@
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>24</v>
       </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="9" t="str">
-        <v>今日积分榜单已更新，看看自己排在第几？往前多冲几名，奖励又近一步！</v>
-      </c>
-      <c r="D27" s="9" t="str">
-        <v>积分就是努力的证明！越活跃，越瘦得快，越能拿大奖！家人们，冲就完事了！</v>
-      </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -2080,19 +2394,19 @@
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>25</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="9" t="str">
-        <v>群内积分靠大家一起活跃，你多出现一次，排名就多一份希望，一起动起来！</v>
-      </c>
-      <c r="D28" s="9" t="str">
-        <v>结营倒计时 XX 天！前 6 名稳住，后 6 名逆袭，中间的伙伴往前冲，咱们一起健康减重，一起拿奖！</v>
-      </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -2108,24 +2422,23 @@
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>26</v>
       </c>
-      <c r="B29" s="6" t="str">
-        <v>【反向激励专属话术】
-（适配后 6 名「绿草莓奖」幽默激励）</v>
-      </c>
-      <c r="C29" s="8" t="str" xml:space="preserve">
-        <v> 正式版</v>
-      </c>
-      <c r="D29" s="7" t="str">
-        <v>温柔版</v>
-      </c>
-      <c r="E29" s="8" t="str">
-        <v>活泼版</v>
-      </c>
-      <c r="F29" s="8"/>
+      <c r="B29" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="7"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -2141,22 +2454,19 @@
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:20" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>27</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="4" t="str">
-        <v>个人积分榜后 6 名的伙伴请注意：
-本次结营设置「绿草莓奖」幽默反向激励，希望大家以此为契机，重新调整减重节奏，跟上每日打卡、学习的进度，在后续的健康管理中迎头赶上，收获理想的减重成果。</v>
-      </c>
-      <c r="D30" s="4" t="str">
-        <v>积分暂时靠后的小伙伴们别灰心呀～
-3 个月的旅程还没结束，现在开始行动，积分和体重都能追上来！我们一起慢慢调整，互相陪伴，下一次榜单一定能看到你们的进步！</v>
-      </c>
-      <c r="E30" s="4" t="str">
-        <v>家人们！后 6 名的「绿草莓奖」已经就位！
-别摆烂了！再不打卡、再不减重，就要拿反向奖励了！赶紧动起来，把积分冲上去，把体重降下来，逆袭就在下一个榜单！</v>
+      <c r="B30" s="30"/>
+      <c r="C30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="1"/>
@@ -2174,7 +2484,7 @@
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="1"/>
@@ -2196,7 +2506,7 @@
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="1"/>
@@ -2218,7 +2528,7 @@
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="1"/>
@@ -2240,7 +2550,7 @@
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="1"/>
@@ -2262,7 +2572,7 @@
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="1"/>
@@ -2284,7 +2594,7 @@
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="1"/>
@@ -2306,7 +2616,7 @@
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="1"/>
@@ -2328,7 +2638,7 @@
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="1"/>
@@ -2350,7 +2660,7 @@
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="1"/>
@@ -2372,7 +2682,7 @@
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="1"/>
@@ -2394,7 +2704,7 @@
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="1"/>
@@ -2416,7 +2726,7 @@
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="1"/>
@@ -2438,7 +2748,7 @@
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="1"/>
@@ -2460,7 +2770,7 @@
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="1"/>
@@ -2482,7 +2792,7 @@
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="1"/>
@@ -2504,7 +2814,7 @@
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="1"/>
@@ -2526,7 +2836,7 @@
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="1"/>
@@ -2548,7 +2858,7 @@
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="1"/>
@@ -2570,7 +2880,7 @@
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="1"/>
@@ -2592,7 +2902,7 @@
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="1"/>
@@ -2614,7 +2924,7 @@
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="1"/>
@@ -2636,7 +2946,7 @@
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="1"/>
@@ -2658,7 +2968,7 @@
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="1"/>
@@ -2680,7 +2990,7 @@
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="1"/>
@@ -2702,7 +3012,7 @@
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="1"/>
@@ -2724,7 +3034,7 @@
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="1"/>
@@ -2746,7 +3056,7 @@
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="1"/>
@@ -2768,7 +3078,7 @@
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="1"/>
@@ -2790,7 +3100,7 @@
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="1"/>
@@ -2812,7 +3122,7 @@
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="1"/>
@@ -2834,7 +3144,7 @@
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="1"/>
@@ -2856,7 +3166,7 @@
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="1"/>
@@ -2878,7 +3188,7 @@
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="1"/>
@@ -2900,7 +3210,7 @@
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="1"/>
@@ -2922,7 +3232,7 @@
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="1"/>
@@ -2944,7 +3254,7 @@
       <c r="S65" s="1"/>
       <c r="T65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="1"/>
@@ -2966,7 +3276,7 @@
       <c r="S66" s="1"/>
       <c r="T66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="1"/>
@@ -2988,7 +3298,7 @@
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="1"/>
@@ -3010,7 +3320,7 @@
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="1"/>
@@ -3032,7 +3342,7 @@
       <c r="S69" s="1"/>
       <c r="T69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="1"/>
@@ -3054,7 +3364,7 @@
       <c r="S70" s="1"/>
       <c r="T70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="1"/>
@@ -3076,7 +3386,7 @@
       <c r="S71" s="1"/>
       <c r="T71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="1"/>
@@ -3098,7 +3408,7 @@
       <c r="S72" s="1"/>
       <c r="T72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="1"/>
@@ -3120,7 +3430,7 @@
       <c r="S73" s="1"/>
       <c r="T73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="1"/>
@@ -3142,7 +3452,7 @@
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="1"/>
@@ -3164,7 +3474,7 @@
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="1"/>
@@ -3186,7 +3496,7 @@
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="1"/>
@@ -3208,7 +3518,7 @@
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="1"/>
@@ -3230,7 +3540,7 @@
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="1"/>
@@ -3252,7 +3562,7 @@
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="1"/>
@@ -3274,7 +3584,7 @@
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="1"/>
@@ -3296,7 +3606,7 @@
       <c r="S81" s="1"/>
       <c r="T81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="1"/>
@@ -3318,7 +3628,7 @@
       <c r="S82" s="1"/>
       <c r="T82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="1"/>
@@ -3340,7 +3650,7 @@
       <c r="S83" s="1"/>
       <c r="T83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="1"/>
@@ -3362,7 +3672,7 @@
       <c r="S84" s="1"/>
       <c r="T84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="1"/>
@@ -3384,7 +3694,7 @@
       <c r="S85" s="1"/>
       <c r="T85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="1"/>
@@ -3406,7 +3716,7 @@
       <c r="S86" s="1"/>
       <c r="T86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="1"/>
@@ -3428,7 +3738,7 @@
       <c r="S87" s="1"/>
       <c r="T87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="1"/>
@@ -3450,7 +3760,7 @@
       <c r="S88" s="1"/>
       <c r="T88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="1"/>
@@ -3472,7 +3782,7 @@
       <c r="S89" s="1"/>
       <c r="T89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="1"/>
@@ -3494,7 +3804,7 @@
       <c r="S90" s="1"/>
       <c r="T90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="1"/>
@@ -3516,7 +3826,7 @@
       <c r="S91" s="1"/>
       <c r="T91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="1"/>
@@ -3538,7 +3848,7 @@
       <c r="S92" s="1"/>
       <c r="T92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="1"/>
@@ -3560,7 +3870,7 @@
       <c r="S93" s="1"/>
       <c r="T93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="1"/>
@@ -3582,7 +3892,7 @@
       <c r="S94" s="1"/>
       <c r="T94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="1"/>
@@ -3604,7 +3914,7 @@
       <c r="S95" s="1"/>
       <c r="T95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="1"/>
@@ -3626,7 +3936,7 @@
       <c r="S96" s="1"/>
       <c r="T96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="1"/>
@@ -3648,7 +3958,7 @@
       <c r="S97" s="1"/>
       <c r="T97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="1"/>
@@ -3670,7 +3980,7 @@
       <c r="S98" s="1"/>
       <c r="T98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="1"/>
@@ -3692,7 +4002,7 @@
       <c r="S99" s="1"/>
       <c r="T99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="1"/>
@@ -3714,7 +4024,7 @@
       <c r="S100" s="1"/>
       <c r="T100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="1"/>
@@ -3736,7 +4046,7 @@
       <c r="S101" s="1"/>
       <c r="T101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="1"/>
@@ -3758,7 +4068,7 @@
       <c r="S102" s="1"/>
       <c r="T102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="1"/>
@@ -3780,7 +4090,7 @@
       <c r="S103" s="1"/>
       <c r="T103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="1"/>
@@ -3802,7 +4112,7 @@
       <c r="S104" s="1"/>
       <c r="T104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="1"/>
@@ -3824,7 +4134,7 @@
       <c r="S105" s="1"/>
       <c r="T105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="1"/>
@@ -3846,7 +4156,7 @@
       <c r="S106" s="1"/>
       <c r="T106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="1"/>
@@ -3868,7 +4178,7 @@
       <c r="S107" s="1"/>
       <c r="T107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="1"/>
@@ -3890,7 +4200,7 @@
       <c r="S108" s="1"/>
       <c r="T108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="1"/>
@@ -3912,7 +4222,7 @@
       <c r="S109" s="1"/>
       <c r="T109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="1"/>
@@ -3934,7 +4244,7 @@
       <c r="S110" s="1"/>
       <c r="T110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="1"/>
@@ -3956,7 +4266,7 @@
       <c r="S111" s="1"/>
       <c r="T111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="1"/>
@@ -3978,7 +4288,7 @@
       <c r="S112" s="1"/>
       <c r="T112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="1"/>
@@ -4000,7 +4310,7 @@
       <c r="S113" s="1"/>
       <c r="T113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="1"/>
@@ -4022,7 +4332,7 @@
       <c r="S114" s="1"/>
       <c r="T114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="1"/>
@@ -4044,7 +4354,7 @@
       <c r="S115" s="1"/>
       <c r="T115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="1"/>
@@ -4066,7 +4376,7 @@
       <c r="S116" s="1"/>
       <c r="T116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="1"/>
@@ -4088,7 +4398,7 @@
       <c r="S117" s="1"/>
       <c r="T117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="1"/>
@@ -4110,7 +4420,7 @@
       <c r="S118" s="1"/>
       <c r="T118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="1"/>
@@ -4132,7 +4442,7 @@
       <c r="S119" s="1"/>
       <c r="T119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="1"/>
@@ -4154,7 +4464,7 @@
       <c r="S120" s="1"/>
       <c r="T120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="1"/>
@@ -4176,7 +4486,7 @@
       <c r="S121" s="1"/>
       <c r="T121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="1"/>
@@ -4198,7 +4508,7 @@
       <c r="S122" s="1"/>
       <c r="T122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="1"/>
@@ -4220,7 +4530,7 @@
       <c r="S123" s="1"/>
       <c r="T123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="1"/>
@@ -4242,7 +4552,7 @@
       <c r="S124" s="1"/>
       <c r="T124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="1"/>
@@ -4264,7 +4574,7 @@
       <c r="S125" s="1"/>
       <c r="T125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="1"/>
@@ -4286,7 +4596,7 @@
       <c r="S126" s="1"/>
       <c r="T126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="1"/>
@@ -4308,7 +4618,7 @@
       <c r="S127" s="1"/>
       <c r="T127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="1"/>
@@ -4330,7 +4640,7 @@
       <c r="S128" s="1"/>
       <c r="T128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="1"/>
@@ -4352,7 +4662,7 @@
       <c r="S129" s="1"/>
       <c r="T129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="1"/>
@@ -4374,7 +4684,7 @@
       <c r="S130" s="1"/>
       <c r="T130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="1"/>
@@ -4396,7 +4706,7 @@
       <c r="S131" s="1"/>
       <c r="T131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="1"/>
@@ -4418,7 +4728,7 @@
       <c r="S132" s="1"/>
       <c r="T132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="1"/>
@@ -4440,7 +4750,7 @@
       <c r="S133" s="1"/>
       <c r="T133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="1"/>
@@ -4462,7 +4772,7 @@
       <c r="S134" s="1"/>
       <c r="T134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="1"/>
@@ -4484,7 +4794,7 @@
       <c r="S135" s="1"/>
       <c r="T135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="1"/>
@@ -4506,7 +4816,7 @@
       <c r="S136" s="1"/>
       <c r="T136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="1"/>
@@ -4528,7 +4838,7 @@
       <c r="S137" s="1"/>
       <c r="T137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="1"/>
@@ -4550,7 +4860,7 @@
       <c r="S138" s="1"/>
       <c r="T138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="1"/>
@@ -4572,7 +4882,7 @@
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="1"/>
@@ -4594,7 +4904,7 @@
       <c r="S140" s="1"/>
       <c r="T140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="1"/>
@@ -4616,7 +4926,7 @@
       <c r="S141" s="1"/>
       <c r="T141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="1"/>
@@ -4638,7 +4948,7 @@
       <c r="S142" s="1"/>
       <c r="T142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="1"/>
@@ -4660,7 +4970,7 @@
       <c r="S143" s="1"/>
       <c r="T143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="1"/>
@@ -4682,7 +4992,7 @@
       <c r="S144" s="1"/>
       <c r="T144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="1"/>
@@ -4704,7 +5014,7 @@
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="1"/>
@@ -4726,7 +5036,7 @@
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="1"/>
@@ -4748,7 +5058,7 @@
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="1"/>
@@ -4770,7 +5080,7 @@
       <c r="S148" s="1"/>
       <c r="T148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="1"/>
@@ -4792,7 +5102,7 @@
       <c r="S149" s="1"/>
       <c r="T149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="1"/>
@@ -4814,7 +5124,7 @@
       <c r="S150" s="1"/>
       <c r="T150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="1"/>
@@ -4836,7 +5146,7 @@
       <c r="S151" s="1"/>
       <c r="T151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="1"/>
@@ -4858,7 +5168,7 @@
       <c r="S152" s="1"/>
       <c r="T152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="C153" s="1"/>
@@ -4880,7 +5190,7 @@
       <c r="S153" s="1"/>
       <c r="T153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="C154" s="1"/>
@@ -4902,7 +5212,7 @@
       <c r="S154" s="1"/>
       <c r="T154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="C155" s="1"/>
@@ -4924,7 +5234,7 @@
       <c r="S155" s="1"/>
       <c r="T155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="1"/>
@@ -4946,7 +5256,7 @@
       <c r="S156" s="1"/>
       <c r="T156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="C157" s="1"/>
@@ -4968,7 +5278,7 @@
       <c r="S157" s="1"/>
       <c r="T157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="C158" s="1"/>
@@ -4990,7 +5300,7 @@
       <c r="S158" s="1"/>
       <c r="T158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="C159" s="1"/>
@@ -5012,7 +5322,7 @@
       <c r="S159" s="1"/>
       <c r="T159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="C160" s="1"/>
@@ -5034,7 +5344,7 @@
       <c r="S160" s="1"/>
       <c r="T160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="C161" s="1"/>
@@ -5056,7 +5366,7 @@
       <c r="S161" s="1"/>
       <c r="T161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="C162" s="1"/>
@@ -5078,7 +5388,7 @@
       <c r="S162" s="1"/>
       <c r="T162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="C163" s="1"/>
@@ -5100,7 +5410,7 @@
       <c r="S163" s="1"/>
       <c r="T163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="C164" s="1"/>
@@ -5122,7 +5432,7 @@
       <c r="S164" s="1"/>
       <c r="T164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="C165" s="1"/>
@@ -5144,7 +5454,7 @@
       <c r="S165" s="1"/>
       <c r="T165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="C166" s="1"/>
@@ -5166,7 +5476,7 @@
       <c r="S166" s="1"/>
       <c r="T166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="1"/>
@@ -5188,7 +5498,7 @@
       <c r="S167" s="1"/>
       <c r="T167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="C168" s="1"/>
@@ -5210,7 +5520,7 @@
       <c r="S168" s="1"/>
       <c r="T168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="C169" s="1"/>
@@ -5232,7 +5542,7 @@
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="C170" s="1"/>
@@ -5254,7 +5564,7 @@
       <c r="S170" s="1"/>
       <c r="T170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="C171" s="1"/>
@@ -5276,7 +5586,7 @@
       <c r="S171" s="1"/>
       <c r="T171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="C172" s="1"/>
@@ -5298,7 +5608,7 @@
       <c r="S172" s="1"/>
       <c r="T172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="C173" s="1"/>
@@ -5320,7 +5630,7 @@
       <c r="S173" s="1"/>
       <c r="T173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="C174" s="1"/>
@@ -5342,7 +5652,7 @@
       <c r="S174" s="1"/>
       <c r="T174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="C175" s="1"/>
@@ -5364,7 +5674,7 @@
       <c r="S175" s="1"/>
       <c r="T175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="1"/>
@@ -5386,7 +5696,7 @@
       <c r="S176" s="1"/>
       <c r="T176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="C177" s="1"/>
@@ -5408,7 +5718,7 @@
       <c r="S177" s="1"/>
       <c r="T177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="C178" s="1"/>
@@ -5430,7 +5740,7 @@
       <c r="S178" s="1"/>
       <c r="T178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="C179" s="1"/>
@@ -5452,7 +5762,7 @@
       <c r="S179" s="1"/>
       <c r="T179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="C180" s="1"/>
@@ -5474,7 +5784,7 @@
       <c r="S180" s="1"/>
       <c r="T180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="C181" s="1"/>
@@ -5496,7 +5806,7 @@
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="C182" s="1"/>
@@ -5518,7 +5828,7 @@
       <c r="S182" s="1"/>
       <c r="T182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="C183" s="1"/>
@@ -5540,7 +5850,7 @@
       <c r="S183" s="1"/>
       <c r="T183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="C184" s="1"/>
@@ -5562,7 +5872,7 @@
       <c r="S184" s="1"/>
       <c r="T184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="C185" s="1"/>
@@ -5584,7 +5894,7 @@
       <c r="S185" s="1"/>
       <c r="T185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="1"/>
@@ -5606,7 +5916,7 @@
       <c r="S186" s="1"/>
       <c r="T186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="C187" s="1"/>
@@ -5628,7 +5938,7 @@
       <c r="S187" s="1"/>
       <c r="T187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="1"/>
@@ -5650,7 +5960,7 @@
       <c r="S188" s="1"/>
       <c r="T188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="C189" s="1"/>
@@ -5672,7 +5982,7 @@
       <c r="S189" s="1"/>
       <c r="T189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="C190" s="1"/>
@@ -5694,7 +6004,7 @@
       <c r="S190" s="1"/>
       <c r="T190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="C191" s="1"/>
@@ -5716,7 +6026,7 @@
       <c r="S191" s="1"/>
       <c r="T191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="C192" s="1"/>
@@ -5738,7 +6048,7 @@
       <c r="S192" s="1"/>
       <c r="T192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="C193" s="1"/>
@@ -5760,7 +6070,7 @@
       <c r="S193" s="1"/>
       <c r="T193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="C194" s="1"/>
@@ -5782,7 +6092,7 @@
       <c r="S194" s="1"/>
       <c r="T194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="C195" s="1"/>
@@ -5804,7 +6114,7 @@
       <c r="S195" s="1"/>
       <c r="T195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="1"/>
@@ -5826,7 +6136,7 @@
       <c r="S196" s="1"/>
       <c r="T196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="1"/>
@@ -5848,7 +6158,7 @@
       <c r="S197" s="1"/>
       <c r="T197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="3"/>
       <c r="C198" s="1"/>
@@ -5870,7 +6180,7 @@
       <c r="S198" s="1"/>
       <c r="T198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="3"/>
       <c r="C199" s="1"/>
@@ -5892,7 +6202,7 @@
       <c r="S199" s="1"/>
       <c r="T199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="3"/>
       <c r="C200" s="1"/>
@@ -5914,7 +6224,7 @@
       <c r="S200" s="1"/>
       <c r="T200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="3"/>
       <c r="C201" s="1"/>
@@ -5937,7 +6247,7 @@
       <c r="T201" s="1"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B29:B30"/>
@@ -5950,984 +6260,962 @@
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B4:B7"/>
   </mergeCells>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{999FCE7B-B3AC-4E1D-9D45-AF3A1521A42F}">
   <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="19"/>
+  <dimension ref="A1:G199"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="41"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="76"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="6" min="6" style="0" width="40"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="41" customWidth="1"/>
+    <col min="5" max="5" width="76" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="32" t="str">
-        <v>减重健康群・积分激励运营
-发榜时间：每日早 8:00 早安分享后立即发送</v>
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>71</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="21"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="30" t="str">
-        <v>阶段节点</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30" t="str">
-        <v>执行时间</v>
-      </c>
-      <c r="D2" s="30" t="str">
-        <v>核心动作</v>
-      </c>
-      <c r="E2" s="31" t="str">
-        <v>群内话术（可直接复制）</v>
-      </c>
-      <c r="F2" s="31" t="str">
-        <v>配套 1v1 动作</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="26">
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="100.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="26" t="str">
-        <v>第一阶段：每日发榜（日常运营）</v>
-      </c>
-      <c r="C3" s="27" t="str">
-        <v>每日早 8:00早安后立刻发</v>
-      </c>
-      <c r="D3" s="25" t="str">
-        <v>1. 发今日积分榜
-2. 表扬前 6 名
-3. 表扬连续打卡
-4. 鼓励回归用户
-5. 提醒潜水成员
-6. 提社群月度 PK</v>
-      </c>
-      <c r="E3" s="24" t="s">
+      <c r="B3" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:7" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
         <v>2</v>
       </c>
-      <c r="F3" s="25" t="str">
-        <v>1. 私发 TOP3：鼓励稳住排名
-2. 私发连续打卡：肯定坚持
-3. 私发 3 天未打卡：温和提醒</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="22">
-        <v>2</v>
-      </c>
-      <c r="B4" s="22" t="str">
-        <v>第二阶段：每周复盘（深度激活）</v>
-      </c>
-      <c r="C4" s="23" t="str">
-        <v>每周日晚 19:30</v>
-      </c>
-      <c r="D4" s="20" t="str">
-        <v>1. 本周积分总结
-2. 表扬周 TOP6
-3. 表扬积分暴涨用户
-4. 鼓励掉队回归
-5. 同步社群 PK 排名
-6. 轻科普减重知识点</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="20" t="str">
-        <v>1. 表扬进步最快用户
-2. 邀请减重效果好的分享
-3. 连续 2 周未打卡：1v1 关怀</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="26">
+      <c r="B4" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="26" t="str">
-        <v>结营冲刺
-（前 14～7 天）</v>
-      </c>
-      <c r="C5" s="27" t="str">
-        <v>每日早 8:00</v>
-      </c>
-      <c r="D5" s="25" t="str">
-        <v>倒计时提醒 + 动员前 6 稳住、中间冲刺、后段逆袭</v>
-      </c>
-      <c r="E5" s="25" t="str">
-        <v>@所有人
- ⚡金百花奖冲刺倒计时 XX 天前 6 名的伙伴继续稳住，别被反超！
-中间梯队再冲一冲，完全有机会进前 6！暂时靠后的伙伴正是逆袭好时机，每天打卡就能追分！
-社群 PK 最后冲刺，一起为团队争光！</v>
-      </c>
-      <c r="F5" s="25" t="str">
-        <v>重点用户群内 @提醒</v>
-      </c>
-      <c r="G5" s="21"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="22">
+      <c r="B5" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
         <v>4</v>
       </c>
-      <c r="B6" s="22" t="str">
-        <v>结营冲刺
-（前 7～3 天）</v>
-      </c>
-      <c r="C6" s="23" t="str">
-        <v>早 8:00 发榜 +晚再补一条冲刺</v>
-      </c>
-      <c r="D6" s="20" t="str">
-        <v>早晚双重动员强化紧迫感</v>
-      </c>
-      <c r="E6" s="20" t="str">
-        <v>早 8:00：早安～今日积分榜已更新！冲刺最后阶段，每一分都关键，前 6 稳住、中间猛冲、后面逆袭！
-晚提醒：最后 XX 天冲金百花奖！今天多打卡、多互动，排名就能再往前，大奖近在眼前！</v>
-      </c>
-      <c r="F6" s="20" t="str">
-        <v>对差几分进前 6 的用户群内艾特鼓励</v>
-      </c>
-      <c r="G6" s="21"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="26">
+      <c r="B6" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
         <v>5</v>
       </c>
-      <c r="B7" s="26" t="str">
-        <v>结营前 1 天</v>
-      </c>
-      <c r="C7" s="27" t="str">
-        <v>早 8:00</v>
-      </c>
-      <c r="D7" s="25" t="str">
-        <v>最终冲刺提醒最后打卡号召</v>
-      </c>
-      <c r="E7" s="25" t="str">
-        <v>@所有人 
-🎉最后 1 天冲刺！今天的打卡将决定最终排名，前 6 名稳住阵脚，所有人再努力一把，不留遗憾！感谢一路陪伴，明天公布最终榜单与金百花奖、绿草莓奖、社群 PK 大奖！</v>
-      </c>
-      <c r="F7" s="25" t="str">
-        <v>群内@用户 提醒 TOP10 务必打卡</v>
-      </c>
-      <c r="G7" s="21"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="22">
+      <c r="B7" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="22" t="str">
-        <v>结营当天</v>
-      </c>
-      <c r="C8" s="23" t="str">
-        <v>早 8:00</v>
-      </c>
-      <c r="D8" s="20" t="str">
-        <v>公布最终榜单获奖公示</v>
-      </c>
-      <c r="E8" s="20" t="str">
-        <v>@所有人 🎊3 个月结营・最终积分榜单公布
-🏆金百花奖（前 6）：XX🍀
-绿草莓奖（后 6）：XX
-团队月度 PK 获奖社群：XX
-感谢大家的坚持，减重不是终点，而是健康生活的开始！</v>
-      </c>
-      <c r="F8" s="20" t="str">
-        <v>获奖用户恭喜【绿草莓用户】温柔鼓励</v>
-      </c>
-      <c r="G8" s="21"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="29"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="29"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-    </row>
-    <row r="55">
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-    </row>
-    <row r="59">
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-    </row>
-    <row r="60">
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-    </row>
-    <row r="61">
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-    </row>
-    <row r="63">
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-    </row>
-    <row r="64">
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-    </row>
-    <row r="65">
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-    </row>
-    <row r="66">
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-    </row>
-    <row r="67">
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-    </row>
-    <row r="68">
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-    </row>
-    <row r="69">
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-    </row>
-    <row r="70">
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-    </row>
-    <row r="71">
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
-    </row>
-    <row r="72">
-      <c r="B72" s="19"/>
-      <c r="C72" s="19"/>
-    </row>
-    <row r="73">
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-    </row>
-    <row r="74">
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-    </row>
-    <row r="75">
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-    </row>
-    <row r="76">
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-    </row>
-    <row r="77">
-      <c r="B77" s="19"/>
-      <c r="C77" s="19"/>
-    </row>
-    <row r="78">
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-    </row>
-    <row r="79">
-      <c r="B79" s="19"/>
-      <c r="C79" s="19"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="19"/>
-      <c r="C80" s="19"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
-    </row>
-    <row r="82">
-      <c r="B82" s="19"/>
-      <c r="C82" s="19"/>
-    </row>
-    <row r="83">
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
-    </row>
-    <row r="84">
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-    </row>
-    <row r="85">
-      <c r="B85" s="19"/>
-      <c r="C85" s="19"/>
-    </row>
-    <row r="86">
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-    </row>
-    <row r="87">
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="19"/>
-      <c r="C90" s="19"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-    </row>
-    <row r="93">
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="19"/>
-      <c r="C94" s="19"/>
-    </row>
-    <row r="95">
-      <c r="B95" s="19"/>
-      <c r="C95" s="19"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="19"/>
-      <c r="C96" s="19"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-    </row>
-    <row r="98">
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-    </row>
-    <row r="100">
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="19"/>
-      <c r="C101" s="19"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="19"/>
-      <c r="C102" s="19"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="19"/>
-      <c r="C104" s="19"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="19"/>
-      <c r="C105" s="19"/>
-    </row>
-    <row r="106">
-      <c r="B106" s="19"/>
-      <c r="C106" s="19"/>
-    </row>
-    <row r="107">
-      <c r="B107" s="19"/>
-      <c r="C107" s="19"/>
-    </row>
-    <row r="108">
-      <c r="B108" s="19"/>
-      <c r="C108" s="19"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="19"/>
-      <c r="C109" s="19"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="19"/>
-      <c r="C110" s="19"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-    </row>
-    <row r="112">
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="19"/>
-      <c r="C113" s="19"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="19"/>
-      <c r="C114" s="19"/>
-    </row>
-    <row r="115">
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
-    </row>
-    <row r="116">
-      <c r="B116" s="19"/>
-      <c r="C116" s="19"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="19"/>
-      <c r="C117" s="19"/>
-    </row>
-    <row r="118">
-      <c r="B118" s="19"/>
-      <c r="C118" s="19"/>
-    </row>
-    <row r="119">
-      <c r="B119" s="19"/>
-      <c r="C119" s="19"/>
-    </row>
-    <row r="120">
-      <c r="B120" s="19"/>
-      <c r="C120" s="19"/>
-    </row>
-    <row r="121">
-      <c r="B121" s="19"/>
-      <c r="C121" s="19"/>
-    </row>
-    <row r="122">
-      <c r="B122" s="19"/>
-      <c r="C122" s="19"/>
-    </row>
-    <row r="123">
-      <c r="B123" s="19"/>
-      <c r="C123" s="19"/>
-    </row>
-    <row r="124">
-      <c r="B124" s="19"/>
-      <c r="C124" s="19"/>
-    </row>
-    <row r="125">
-      <c r="B125" s="19"/>
-      <c r="C125" s="19"/>
-    </row>
-    <row r="126">
-      <c r="B126" s="19"/>
-      <c r="C126" s="19"/>
-    </row>
-    <row r="127">
-      <c r="B127" s="19"/>
-      <c r="C127" s="19"/>
-    </row>
-    <row r="128">
-      <c r="B128" s="19"/>
-      <c r="C128" s="19"/>
-    </row>
-    <row r="129">
-      <c r="B129" s="19"/>
-      <c r="C129" s="19"/>
-    </row>
-    <row r="130">
-      <c r="B130" s="19"/>
-      <c r="C130" s="19"/>
-    </row>
-    <row r="131">
-      <c r="B131" s="19"/>
-      <c r="C131" s="19"/>
-    </row>
-    <row r="132">
-      <c r="B132" s="19"/>
-      <c r="C132" s="19"/>
-    </row>
-    <row r="133">
-      <c r="B133" s="19"/>
-      <c r="C133" s="19"/>
-    </row>
-    <row r="134">
-      <c r="B134" s="19"/>
-      <c r="C134" s="19"/>
-    </row>
-    <row r="135">
-      <c r="B135" s="19"/>
-      <c r="C135" s="19"/>
-    </row>
-    <row r="136">
-      <c r="B136" s="19"/>
-      <c r="C136" s="19"/>
-    </row>
-    <row r="137">
-      <c r="B137" s="19"/>
-      <c r="C137" s="19"/>
-    </row>
-    <row r="138">
-      <c r="B138" s="19"/>
-      <c r="C138" s="19"/>
-    </row>
-    <row r="139">
-      <c r="B139" s="19"/>
-      <c r="C139" s="19"/>
-    </row>
-    <row r="140">
-      <c r="B140" s="19"/>
-      <c r="C140" s="19"/>
-    </row>
-    <row r="141">
-      <c r="B141" s="19"/>
-      <c r="C141" s="19"/>
-    </row>
-    <row r="142">
-      <c r="B142" s="19"/>
-      <c r="C142" s="19"/>
-    </row>
-    <row r="143">
-      <c r="B143" s="19"/>
-      <c r="C143" s="19"/>
-    </row>
-    <row r="144">
-      <c r="B144" s="19"/>
-      <c r="C144" s="19"/>
-    </row>
-    <row r="145">
-      <c r="B145" s="19"/>
-      <c r="C145" s="19"/>
-    </row>
-    <row r="146">
-      <c r="B146" s="19"/>
-      <c r="C146" s="19"/>
-    </row>
-    <row r="147">
-      <c r="B147" s="19"/>
-      <c r="C147" s="19"/>
-    </row>
-    <row r="148">
-      <c r="B148" s="19"/>
-      <c r="C148" s="19"/>
-    </row>
-    <row r="149">
-      <c r="B149" s="19"/>
-      <c r="C149" s="19"/>
-    </row>
-    <row r="150">
-      <c r="B150" s="19"/>
-      <c r="C150" s="19"/>
-    </row>
-    <row r="151">
-      <c r="B151" s="19"/>
-      <c r="C151" s="19"/>
-    </row>
-    <row r="152">
-      <c r="B152" s="19"/>
-      <c r="C152" s="19"/>
-    </row>
-    <row r="153">
-      <c r="B153" s="19"/>
-      <c r="C153" s="19"/>
-    </row>
-    <row r="154">
-      <c r="B154" s="19"/>
-      <c r="C154" s="19"/>
-    </row>
-    <row r="155">
-      <c r="B155" s="19"/>
-      <c r="C155" s="19"/>
-    </row>
-    <row r="156">
-      <c r="B156" s="19"/>
-      <c r="C156" s="19"/>
-    </row>
-    <row r="157">
-      <c r="B157" s="19"/>
-      <c r="C157" s="19"/>
-    </row>
-    <row r="158">
-      <c r="B158" s="19"/>
-      <c r="C158" s="19"/>
-    </row>
-    <row r="159">
-      <c r="B159" s="19"/>
-      <c r="C159" s="19"/>
-    </row>
-    <row r="160">
-      <c r="B160" s="19"/>
-      <c r="C160" s="19"/>
-    </row>
-    <row r="161">
-      <c r="B161" s="19"/>
-      <c r="C161" s="19"/>
-    </row>
-    <row r="162">
-      <c r="B162" s="19"/>
-      <c r="C162" s="19"/>
-    </row>
-    <row r="163">
-      <c r="B163" s="19"/>
-      <c r="C163" s="19"/>
-    </row>
-    <row r="164">
-      <c r="B164" s="19"/>
-      <c r="C164" s="19"/>
-    </row>
-    <row r="165">
-      <c r="B165" s="19"/>
-      <c r="C165" s="19"/>
-    </row>
-    <row r="166">
-      <c r="B166" s="19"/>
-      <c r="C166" s="19"/>
-    </row>
-    <row r="167">
-      <c r="B167" s="19"/>
-      <c r="C167" s="19"/>
-    </row>
-    <row r="168">
-      <c r="B168" s="19"/>
-      <c r="C168" s="19"/>
-    </row>
-    <row r="169">
-      <c r="B169" s="19"/>
-      <c r="C169" s="19"/>
-    </row>
-    <row r="170">
-      <c r="B170" s="19"/>
-      <c r="C170" s="19"/>
-    </row>
-    <row r="171">
-      <c r="B171" s="19"/>
-      <c r="C171" s="19"/>
-    </row>
-    <row r="172">
-      <c r="B172" s="19"/>
-      <c r="C172" s="19"/>
-    </row>
-    <row r="173">
-      <c r="B173" s="19"/>
-      <c r="C173" s="19"/>
-    </row>
-    <row r="174">
-      <c r="B174" s="19"/>
-      <c r="C174" s="19"/>
-    </row>
-    <row r="175">
-      <c r="B175" s="19"/>
-      <c r="C175" s="19"/>
-    </row>
-    <row r="176">
-      <c r="B176" s="19"/>
-      <c r="C176" s="19"/>
-    </row>
-    <row r="177">
-      <c r="B177" s="19"/>
-      <c r="C177" s="19"/>
-    </row>
-    <row r="178">
-      <c r="B178" s="19"/>
-      <c r="C178" s="19"/>
-    </row>
-    <row r="179">
-      <c r="B179" s="19"/>
-      <c r="C179" s="19"/>
-    </row>
-    <row r="180">
-      <c r="B180" s="19"/>
-      <c r="C180" s="19"/>
-    </row>
-    <row r="181">
-      <c r="B181" s="19"/>
-      <c r="C181" s="19"/>
-    </row>
-    <row r="182">
-      <c r="B182" s="19"/>
-      <c r="C182" s="19"/>
-    </row>
-    <row r="183">
-      <c r="B183" s="19"/>
-      <c r="C183" s="19"/>
-    </row>
-    <row r="184">
-      <c r="B184" s="19"/>
-      <c r="C184" s="19"/>
-    </row>
-    <row r="185">
-      <c r="B185" s="19"/>
-      <c r="C185" s="19"/>
-    </row>
-    <row r="186">
-      <c r="B186" s="19"/>
-      <c r="C186" s="19"/>
-    </row>
-    <row r="187">
-      <c r="B187" s="19"/>
-      <c r="C187" s="19"/>
-    </row>
-    <row r="188">
-      <c r="B188" s="19"/>
-      <c r="C188" s="19"/>
-    </row>
-    <row r="189">
-      <c r="B189" s="19"/>
-      <c r="C189" s="19"/>
-    </row>
-    <row r="190">
-      <c r="B190" s="19"/>
-      <c r="C190" s="19"/>
-    </row>
-    <row r="191">
-      <c r="B191" s="19"/>
-      <c r="C191" s="19"/>
-    </row>
-    <row r="192">
-      <c r="B192" s="19"/>
-      <c r="C192" s="19"/>
-    </row>
-    <row r="193">
-      <c r="B193" s="19"/>
-      <c r="C193" s="19"/>
-    </row>
-    <row r="194">
-      <c r="B194" s="19"/>
-      <c r="C194" s="19"/>
-    </row>
-    <row r="195">
-      <c r="B195" s="19"/>
-      <c r="C195" s="19"/>
-    </row>
-    <row r="196">
-      <c r="B196" s="19"/>
-      <c r="C196" s="19"/>
-    </row>
-    <row r="197">
-      <c r="B197" s="19"/>
-      <c r="C197" s="19"/>
-    </row>
-    <row r="198">
-      <c r="B198" s="19"/>
-      <c r="C198" s="19"/>
-    </row>
-    <row r="199">
-      <c r="B199" s="19"/>
-      <c r="C199" s="19"/>
+      <c r="B8" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B86" s="12"/>
+      <c r="C86" s="12"/>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B89" s="12"/>
+      <c r="C89" s="12"/>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="12"/>
+      <c r="C90" s="12"/>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B96" s="12"/>
+      <c r="C96" s="12"/>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B97" s="12"/>
+      <c r="C97" s="12"/>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99" s="12"/>
+      <c r="C99" s="12"/>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B100" s="12"/>
+      <c r="C100" s="12"/>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" s="12"/>
+      <c r="C101" s="12"/>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" s="12"/>
+      <c r="C102" s="12"/>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B103" s="12"/>
+      <c r="C103" s="12"/>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B104" s="12"/>
+      <c r="C104" s="12"/>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B105" s="12"/>
+      <c r="C105" s="12"/>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="12"/>
+      <c r="C107" s="12"/>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B109" s="12"/>
+      <c r="C109" s="12"/>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B112" s="12"/>
+      <c r="C112" s="12"/>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" s="12"/>
+      <c r="C113" s="12"/>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" s="12"/>
+      <c r="C114" s="12"/>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" s="12"/>
+      <c r="C116" s="12"/>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B118" s="12"/>
+      <c r="C118" s="12"/>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B119" s="12"/>
+      <c r="C119" s="12"/>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" s="12"/>
+      <c r="C120" s="12"/>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" s="12"/>
+      <c r="C121" s="12"/>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B122" s="12"/>
+      <c r="C122" s="12"/>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" s="12"/>
+      <c r="C123" s="12"/>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B124" s="12"/>
+      <c r="C124" s="12"/>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B125" s="12"/>
+      <c r="C125" s="12"/>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" s="12"/>
+      <c r="C126" s="12"/>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127" s="12"/>
+      <c r="C127" s="12"/>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B128" s="12"/>
+      <c r="C128" s="12"/>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B129" s="12"/>
+      <c r="C129" s="12"/>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B130" s="12"/>
+      <c r="C130" s="12"/>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B131" s="12"/>
+      <c r="C131" s="12"/>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B132" s="12"/>
+      <c r="C132" s="12"/>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B133" s="12"/>
+      <c r="C133" s="12"/>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B134" s="12"/>
+      <c r="C134" s="12"/>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B135" s="12"/>
+      <c r="C135" s="12"/>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B136" s="12"/>
+      <c r="C136" s="12"/>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B137" s="12"/>
+      <c r="C137" s="12"/>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B138" s="12"/>
+      <c r="C138" s="12"/>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B139" s="12"/>
+      <c r="C139" s="12"/>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B140" s="12"/>
+      <c r="C140" s="12"/>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B141" s="12"/>
+      <c r="C141" s="12"/>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B142" s="12"/>
+      <c r="C142" s="12"/>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B143" s="12"/>
+      <c r="C143" s="12"/>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B144" s="12"/>
+      <c r="C144" s="12"/>
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B145" s="12"/>
+      <c r="C145" s="12"/>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B146" s="12"/>
+      <c r="C146" s="12"/>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B147" s="12"/>
+      <c r="C147" s="12"/>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B148" s="12"/>
+      <c r="C148" s="12"/>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B149" s="12"/>
+      <c r="C149" s="12"/>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B150" s="12"/>
+      <c r="C150" s="12"/>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B151" s="12"/>
+      <c r="C151" s="12"/>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B152" s="12"/>
+      <c r="C152" s="12"/>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B153" s="12"/>
+      <c r="C153" s="12"/>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B154" s="12"/>
+      <c r="C154" s="12"/>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B155" s="12"/>
+      <c r="C155" s="12"/>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B156" s="12"/>
+      <c r="C156" s="12"/>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B157" s="12"/>
+      <c r="C157" s="12"/>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B158" s="12"/>
+      <c r="C158" s="12"/>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B159" s="12"/>
+      <c r="C159" s="12"/>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B160" s="12"/>
+      <c r="C160" s="12"/>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B161" s="12"/>
+      <c r="C161" s="12"/>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B162" s="12"/>
+      <c r="C162" s="12"/>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B163" s="12"/>
+      <c r="C163" s="12"/>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B164" s="12"/>
+      <c r="C164" s="12"/>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B165" s="12"/>
+      <c r="C165" s="12"/>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B166" s="12"/>
+      <c r="C166" s="12"/>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B167" s="12"/>
+      <c r="C167" s="12"/>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B168" s="12"/>
+      <c r="C168" s="12"/>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B169" s="12"/>
+      <c r="C169" s="12"/>
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B170" s="12"/>
+      <c r="C170" s="12"/>
+    </row>
+    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B171" s="12"/>
+      <c r="C171" s="12"/>
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B172" s="12"/>
+      <c r="C172" s="12"/>
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B173" s="12"/>
+      <c r="C173" s="12"/>
+    </row>
+    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B174" s="12"/>
+      <c r="C174" s="12"/>
+    </row>
+    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B175" s="12"/>
+      <c r="C175" s="12"/>
+    </row>
+    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B176" s="12"/>
+      <c r="C176" s="12"/>
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B177" s="12"/>
+      <c r="C177" s="12"/>
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B178" s="12"/>
+      <c r="C178" s="12"/>
+    </row>
+    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B179" s="12"/>
+      <c r="C179" s="12"/>
+    </row>
+    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B180" s="12"/>
+      <c r="C180" s="12"/>
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B181" s="12"/>
+      <c r="C181" s="12"/>
+    </row>
+    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B182" s="12"/>
+      <c r="C182" s="12"/>
+    </row>
+    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B183" s="12"/>
+      <c r="C183" s="12"/>
+    </row>
+    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B184" s="12"/>
+      <c r="C184" s="12"/>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B185" s="12"/>
+      <c r="C185" s="12"/>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B186" s="12"/>
+      <c r="C186" s="12"/>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B187" s="12"/>
+      <c r="C187" s="12"/>
+    </row>
+    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B188" s="12"/>
+      <c r="C188" s="12"/>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B189" s="12"/>
+      <c r="C189" s="12"/>
+    </row>
+    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B190" s="12"/>
+      <c r="C190" s="12"/>
+    </row>
+    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B191" s="12"/>
+      <c r="C191" s="12"/>
+    </row>
+    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B192" s="12"/>
+      <c r="C192" s="12"/>
+    </row>
+    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B193" s="12"/>
+      <c r="C193" s="12"/>
+    </row>
+    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B194" s="12"/>
+      <c r="C194" s="12"/>
+    </row>
+    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B195" s="12"/>
+      <c r="C195" s="12"/>
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B196" s="12"/>
+      <c r="C196" s="12"/>
+    </row>
+    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B197" s="12"/>
+      <c r="C197" s="12"/>
+    </row>
+    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B198" s="12"/>
+      <c r="C198" s="12"/>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B199" s="12"/>
+      <c r="C199" s="12"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>